--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -14322,6 +14322,405 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>25</v>
+      </c>
+      <c r="O70" t="n">
+        <v>25</v>
+      </c>
+      <c r="P70" t="n">
+        <v>25</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.02042021018914416</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>25</v>
+      </c>
+      <c r="O71" t="n">
+        <v>25</v>
+      </c>
+      <c r="P71" t="n">
+        <v>25</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14355,7 +14754,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14837,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -14448,7 +14847,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -14468,7 +14867,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -14500,7 +14899,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>285</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -14721,6 +14721,405 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>16</v>
+      </c>
+      <c r="O72" t="n">
+        <v>16</v>
+      </c>
+      <c r="P72" t="n">
+        <v>16</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.01306893452105226</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>16</v>
+      </c>
+      <c r="O73" t="n">
+        <v>16</v>
+      </c>
+      <c r="P73" t="n">
+        <v>16</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14754,7 +15153,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -14837,7 +15236,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -14847,7 +15246,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -14867,7 +15266,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -14899,7 +15298,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13439,7 +13439,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15115,6 +15115,405 @@
         </is>
       </c>
       <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>25</v>
+      </c>
+      <c r="O74" t="n">
+        <v>25</v>
+      </c>
+      <c r="P74" t="n">
+        <v>25</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.02042021018914416</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>25</v>
+      </c>
+      <c r="O75" t="n">
+        <v>25</v>
+      </c>
+      <c r="P75" t="n">
+        <v>25</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -15153,7 +15552,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15236,7 +15635,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -15246,7 +15645,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -15266,7 +15665,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -15298,7 +15697,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -15519,6 +15519,405 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>30</v>
+      </c>
+      <c r="O76" t="n">
+        <v>30</v>
+      </c>
+      <c r="P76" t="n">
+        <v>30</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.02450425222697299</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>30</v>
+      </c>
+      <c r="O77" t="n">
+        <v>30</v>
+      </c>
+      <c r="P77" t="n">
+        <v>30</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15552,7 +15951,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -15635,7 +16034,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -15645,7 +16044,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -15665,7 +16064,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -15697,7 +16096,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -15918,6 +15918,405 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>20</v>
+      </c>
+      <c r="O78" t="n">
+        <v>20</v>
+      </c>
+      <c r="P78" t="n">
+        <v>20</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.01633616815131533</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>20</v>
+      </c>
+      <c r="O79" t="n">
+        <v>20</v>
+      </c>
+      <c r="P79" t="n">
+        <v>20</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15951,7 +16350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16433,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -16044,7 +16443,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -16064,7 +16463,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -16096,7 +16495,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>381</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d222/2026-2029.xlsx
+++ b/diseases/d222/2026-2029.xlsx
@@ -16317,6 +16317,405 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>27</v>
+      </c>
+      <c r="O80" t="n">
+        <v>27</v>
+      </c>
+      <c r="P80" t="n">
+        <v>27</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.02205382700427569</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>japanese-spotted-fever</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D222</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>日本斑点热</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>27</v>
+      </c>
+      <c r="O81" t="n">
+        <v>27</v>
+      </c>
+      <c r="P81" t="n">
+        <v>27</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Japanese spotted fever</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Japan NIID Japanese spotted fever notifications.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_JP_JAPANESE_SPOTTED_FEVER_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16350,7 +16749,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16832,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -16443,7 +16842,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -16463,7 +16862,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -16495,7 +16894,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16">
